--- a/JAWAL.xlsx
+++ b/JAWAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lw\compro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A932AE84-4011-411E-8873-AF5762960BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C00C4F2-886E-40F6-A52A-391401D109F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12330" yWindow="1200" windowWidth="17415" windowHeight="13095" xr2:uid="{B561D326-511F-4621-A445-C6936F55FFB3}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Minggu</t>
   </si>
@@ -54,40 +54,15 @@
     <t>Desain UI/UX</t>
   </si>
   <si>
-    <t>1.Rapat kickoff proyek
-2.Identifikasi kebutuhan fitur
-3.Buat sitemap &amp; wireframe awal</t>
-  </si>
-  <si>
-    <t>1.Desain layout homepage &amp; subpage
-2.Review warna, font, dan elemen visual
-3.Revisi desain berdasarkan feedback</t>
-  </si>
-  <si>
-    <t>1.Coding HTML, CSS, JS
-2.Implementasi desain ke web
-3.Uji tampilan responsif</t>
-  </si>
-  <si>
     <t>Development Front-End</t>
   </si>
   <si>
     <t>Development Back-End</t>
   </si>
   <si>
-    <t>1.Setup server &amp; database
-2.Integrasi CMS/API
-3.Fitur kontak &amp; admin panel</t>
-  </si>
-  <si>
     <t>Konten &amp; Copywriting</t>
   </si>
   <si>
-    <t>1.Tulis profil perusahaan
-2.Upload foto produk/layanan
-3.Optimasi SEO dasar</t>
-  </si>
-  <si>
     <t>Testing &amp; Quality Control</t>
   </si>
   <si>
@@ -95,11 +70,6 @@
   </si>
   <si>
     <t>Maintenance Awal</t>
-  </si>
-  <si>
-    <t>`.Uji fungsionalitas &amp; kompatibilitas
-- Perbaikan bug
-- Validasi performa</t>
   </si>
   <si>
     <t>- Launching ke domain resmi
@@ -134,6 +104,51 @@
   </si>
   <si>
     <t>Web terjaga &amp; optimal</t>
+  </si>
+  <si>
+    <t>3–4</t>
+  </si>
+  <si>
+    <t>4–5</t>
+  </si>
+  <si>
+    <t>5–6</t>
+  </si>
+  <si>
+    <t>6–7</t>
+  </si>
+  <si>
+    <t>9–10</t>
+  </si>
+  <si>
+    <t>-Uji fungsionalitas &amp; kompatibilitas
+- Perbaikan bug
+- Validasi performa</t>
+  </si>
+  <si>
+    <t>- Rapat kickoff proyek
+- Identifikasi kebutuhan fitur
+- Buat sitemap &amp; wireframe awal</t>
+  </si>
+  <si>
+    <t>- Desain layout homepage &amp; subpage
+- Review warna, font, dan elemen visual
+- Revisi desain berdasarkan feedback</t>
+  </si>
+  <si>
+    <t>- Coding HTML, CSS, JS
+- Implementasi desain ke web
+- Uji tampilan responsif</t>
+  </si>
+  <si>
+    <t>- Setup server &amp; database
+- Integrasi CMS/API
+- Fitur kontak &amp; admin panel</t>
+  </si>
+  <si>
+    <t>- Tulis profil perusahaan
+- Upload foto produk/layanan
+- Optimasi SEO dasar</t>
   </si>
 </sst>
 </file>
@@ -169,11 +184,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -521,10 +533,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -535,85 +547,94 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
